--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/128.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/128.xlsx
@@ -426,13 +426,13 @@
         <v>-18.75811494638285</v>
       </c>
       <c r="E2">
-        <v>-6.332534088027684</v>
+        <v>-6.051338494521393</v>
       </c>
       <c r="F2">
-        <v>0.07396871531014318</v>
+        <v>0.3807475963369608</v>
       </c>
       <c r="G2">
-        <v>-13.87366986936906</v>
+        <v>-12.59962297130824</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.30106570058851</v>
       </c>
       <c r="E3">
-        <v>-5.672898450174389</v>
+        <v>-5.723852839708696</v>
       </c>
       <c r="F3">
-        <v>0.7715959221789661</v>
+        <v>0.4952962533477384</v>
       </c>
       <c r="G3">
-        <v>-13.39208812031682</v>
+        <v>-12.05576323957123</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.77300063354616</v>
       </c>
       <c r="E4">
-        <v>-6.892633867192385</v>
+        <v>-6.467065993847555</v>
       </c>
       <c r="F4">
-        <v>0.5089604679861499</v>
+        <v>0.7780416052548046</v>
       </c>
       <c r="G4">
-        <v>-12.55067324496458</v>
+        <v>-11.82105218192798</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.20268334640799</v>
       </c>
       <c r="E5">
-        <v>-7.92418401834763</v>
+        <v>-6.855640763023725</v>
       </c>
       <c r="F5">
-        <v>0.5648272778591918</v>
+        <v>0.9102192846632964</v>
       </c>
       <c r="G5">
-        <v>-12.26278820486955</v>
+        <v>-10.46792297202505</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.56430500131642</v>
       </c>
       <c r="E6">
-        <v>-9.276748634958613</v>
+        <v>-8.891303041321743</v>
       </c>
       <c r="F6">
-        <v>0.990169510392426</v>
+        <v>1.459998042090354</v>
       </c>
       <c r="G6">
-        <v>-12.39395201913548</v>
+        <v>-10.59638869167647</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.85579251539574</v>
       </c>
       <c r="E7">
-        <v>-9.963179253515294</v>
+        <v>-8.895025446956048</v>
       </c>
       <c r="F7">
-        <v>1.156811797932711</v>
+        <v>1.222724054427385</v>
       </c>
       <c r="G7">
-        <v>-11.95506637590322</v>
+        <v>-10.79035024427683</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.0772729165694</v>
       </c>
       <c r="E8">
-        <v>-10.49632102691233</v>
+        <v>-10.59183107220811</v>
       </c>
       <c r="F8">
-        <v>1.410945918771448</v>
+        <v>1.46913602522244</v>
       </c>
       <c r="G8">
-        <v>-11.90906965618059</v>
+        <v>-10.14976630351893</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.24736020256787</v>
       </c>
       <c r="E9">
-        <v>-11.05165232294696</v>
+        <v>-10.41689159281779</v>
       </c>
       <c r="F9">
-        <v>1.271573463389115</v>
+        <v>1.534262763583056</v>
       </c>
       <c r="G9">
-        <v>-10.42370732580255</v>
+        <v>-8.606005949828152</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.38154297409343</v>
       </c>
       <c r="E10">
-        <v>-11.95032346129513</v>
+        <v>-12.0002498872297</v>
       </c>
       <c r="F10">
-        <v>1.683107364045633</v>
+        <v>1.054186070906319</v>
       </c>
       <c r="G10">
-        <v>-10.35095146648598</v>
+        <v>-8.269730665585602</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.52132108711405</v>
       </c>
       <c r="E11">
-        <v>-12.58466304334158</v>
+        <v>-12.64051271327818</v>
       </c>
       <c r="F11">
-        <v>1.734908800833742</v>
+        <v>1.972255638968821</v>
       </c>
       <c r="G11">
-        <v>-9.369099938812317</v>
+        <v>-8.635708164406493</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.71833240934261</v>
       </c>
       <c r="E12">
-        <v>-12.7983390893935</v>
+        <v>-13.26358998046755</v>
       </c>
       <c r="F12">
-        <v>1.538787411383467</v>
+        <v>1.733236407387037</v>
       </c>
       <c r="G12">
-        <v>-8.731197539941231</v>
+        <v>-7.553583522893841</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.0294247747864</v>
       </c>
       <c r="E13">
-        <v>-13.74496676748291</v>
+        <v>-12.05069708767514</v>
       </c>
       <c r="F13">
-        <v>1.714171755576978</v>
+        <v>1.659506978493754</v>
       </c>
       <c r="G13">
-        <v>-8.125228663341954</v>
+        <v>-6.92378533950289</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.51539858375151</v>
       </c>
       <c r="E14">
-        <v>-15.22719065188151</v>
+        <v>-14.81000045545087</v>
       </c>
       <c r="F14">
-        <v>2.211618534734254</v>
+        <v>2.131342065586544</v>
       </c>
       <c r="G14">
-        <v>-7.279231992963359</v>
+        <v>-6.389844002201537</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.2013919805029</v>
       </c>
       <c r="E15">
-        <v>-15.3841702033574</v>
+        <v>-16.12289111128065</v>
       </c>
       <c r="F15">
-        <v>2.033703428487871</v>
+        <v>2.14112936814396</v>
       </c>
       <c r="G15">
-        <v>-6.137249377555145</v>
+        <v>-5.4461067853215</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.08141451966282</v>
       </c>
       <c r="E16">
-        <v>-16.15660107179375</v>
+        <v>-16.71476719255718</v>
       </c>
       <c r="F16">
-        <v>2.508192806694938</v>
+        <v>2.70659314895753</v>
       </c>
       <c r="G16">
-        <v>-6.34340697992218</v>
+        <v>-4.236744636552499</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.12509630791016</v>
       </c>
       <c r="E17">
-        <v>-16.32525050078741</v>
+        <v>-17.83520676000898</v>
       </c>
       <c r="F17">
-        <v>2.437828752871963</v>
+        <v>2.555772083512485</v>
       </c>
       <c r="G17">
-        <v>-5.493940857818429</v>
+        <v>-4.409508766064905</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.27625387047822</v>
       </c>
       <c r="E18">
-        <v>-18.30360946899237</v>
+        <v>-18.20850698635728</v>
       </c>
       <c r="F18">
-        <v>2.945963963252541</v>
+        <v>2.536710599114256</v>
       </c>
       <c r="G18">
-        <v>-4.188619236048114</v>
+        <v>-3.198332438340385</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.47710518103973</v>
       </c>
       <c r="E19">
-        <v>-19.27863520758387</v>
+        <v>-19.581581061749</v>
       </c>
       <c r="F19">
-        <v>3.122483824587421</v>
+        <v>3.380434676682368</v>
       </c>
       <c r="G19">
-        <v>-3.903955356762803</v>
+        <v>-3.509477371394327</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.67533115941403</v>
       </c>
       <c r="E20">
-        <v>-19.87268495638408</v>
+        <v>-19.60075462069748</v>
       </c>
       <c r="F20">
-        <v>3.017845207342506</v>
+        <v>3.217000977326763</v>
       </c>
       <c r="G20">
-        <v>-3.456296767851474</v>
+        <v>-3.475497931979247</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.82896872566771</v>
       </c>
       <c r="E21">
-        <v>-19.98046263776663</v>
+        <v>-19.25465693771326</v>
       </c>
       <c r="F21">
-        <v>3.355557824162645</v>
+        <v>3.306515203079232</v>
       </c>
       <c r="G21">
-        <v>-3.649357852065152</v>
+        <v>-3.260577315569761</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.91800051876716</v>
       </c>
       <c r="E22">
-        <v>-21.21221209632698</v>
+        <v>-22.38280451341373</v>
       </c>
       <c r="F22">
-        <v>3.577200634440227</v>
+        <v>3.704624028690569</v>
       </c>
       <c r="G22">
-        <v>-3.240879569611098</v>
+        <v>-1.389096127309906</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.93123767423813</v>
       </c>
       <c r="E23">
-        <v>-21.70457948975895</v>
+        <v>-22.51352344411914</v>
       </c>
       <c r="F23">
-        <v>3.635419247597696</v>
+        <v>3.89121784335356</v>
       </c>
       <c r="G23">
-        <v>-2.753908252420924</v>
+        <v>-1.996902356683478</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.87280392283415</v>
       </c>
       <c r="E24">
-        <v>-22.40063311558193</v>
+        <v>-21.67684711493598</v>
       </c>
       <c r="F24">
-        <v>3.326300441080817</v>
+        <v>4.269126500013467</v>
       </c>
       <c r="G24">
-        <v>-2.092914798413421</v>
+        <v>-2.589751541310623</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.75957657002113</v>
       </c>
       <c r="E25">
-        <v>-22.22599704395013</v>
+        <v>-23.1459157823423</v>
       </c>
       <c r="F25">
-        <v>3.524890828053262</v>
+        <v>3.627730355378238</v>
       </c>
       <c r="G25">
-        <v>-2.601825100892345</v>
+        <v>-2.455816800428329</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.60872579038358</v>
       </c>
       <c r="E26">
-        <v>-21.42577493052871</v>
+        <v>-22.96324619782089</v>
       </c>
       <c r="F26">
-        <v>3.24565813586664</v>
+        <v>3.391351161557492</v>
       </c>
       <c r="G26">
-        <v>-2.9229943658392</v>
+        <v>-1.186037195567629</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.44139135402438</v>
       </c>
       <c r="E27">
-        <v>-23.21291908375979</v>
+        <v>-22.48340003502012</v>
       </c>
       <c r="F27">
-        <v>3.404807910720981</v>
+        <v>3.450512079734648</v>
       </c>
       <c r="G27">
-        <v>-2.040065249424496</v>
+        <v>-1.756616340352097</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.27527147491271</v>
       </c>
       <c r="E28">
-        <v>-22.65726173759661</v>
+        <v>-23.21678640056233</v>
       </c>
       <c r="F28">
-        <v>3.365731550963428</v>
+        <v>3.957152271731051</v>
       </c>
       <c r="G28">
-        <v>-2.745850384578338</v>
+        <v>-2.335455296257046</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.12201708637845</v>
       </c>
       <c r="E29">
-        <v>-22.67015883157045</v>
+        <v>-22.81709422769734</v>
       </c>
       <c r="F29">
-        <v>3.485587998349801</v>
+        <v>3.280325458355609</v>
       </c>
       <c r="G29">
-        <v>-2.497993150598644</v>
+        <v>-2.261696341642084</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.991500149258783</v>
       </c>
       <c r="E30">
-        <v>-22.79060265475246</v>
+        <v>-22.89321787576627</v>
       </c>
       <c r="F30">
-        <v>3.401406110414617</v>
+        <v>3.807401791484843</v>
       </c>
       <c r="G30">
-        <v>-3.079232252019565</v>
+        <v>-2.039406450862181</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.886594824599277</v>
       </c>
       <c r="E31">
-        <v>-21.74743696776754</v>
+        <v>-22.34330716311883</v>
       </c>
       <c r="F31">
-        <v>3.598341524705428</v>
+        <v>4.098935127516683</v>
       </c>
       <c r="G31">
-        <v>-2.708656405444626</v>
+        <v>-3.593303694994213</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.805685738654251</v>
       </c>
       <c r="E32">
-        <v>-22.05216251221769</v>
+        <v>-22.0491012637885</v>
       </c>
       <c r="F32">
-        <v>3.490594092748505</v>
+        <v>3.470271978441586</v>
       </c>
       <c r="G32">
-        <v>-2.870194475033364</v>
+        <v>-2.47225365903081</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.748965352022196</v>
       </c>
       <c r="E33">
-        <v>-20.94019571963423</v>
+        <v>-22.15927450792111</v>
       </c>
       <c r="F33">
-        <v>3.501480487211236</v>
+        <v>3.964229853467149</v>
       </c>
       <c r="G33">
-        <v>-3.758076167574818</v>
+        <v>-3.205092572331576</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.709081822412081</v>
       </c>
       <c r="E34">
-        <v>-21.08411515207201</v>
+        <v>-21.71828718058017</v>
       </c>
       <c r="F34">
-        <v>3.71374300735167</v>
+        <v>3.892587748970415</v>
       </c>
       <c r="G34">
-        <v>-3.51464182243559</v>
+        <v>-3.101985631510976</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.681162485722446</v>
       </c>
       <c r="E35">
-        <v>-20.16207708784425</v>
+        <v>-20.37981064660705</v>
       </c>
       <c r="F35">
-        <v>3.855110932187456</v>
+        <v>3.687991949166624</v>
       </c>
       <c r="G35">
-        <v>-4.392254202714224</v>
+        <v>-3.833079887312546</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.662136908036885</v>
       </c>
       <c r="E36">
-        <v>-20.64197759233311</v>
+        <v>-20.10673460699651</v>
       </c>
       <c r="F36">
-        <v>4.14487526871175</v>
+        <v>4.021075393595933</v>
       </c>
       <c r="G36">
-        <v>-3.556139510770354</v>
+        <v>-3.026068201204409</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.645281783111361</v>
       </c>
       <c r="E37">
-        <v>-19.39481320825065</v>
+        <v>-20.02463337323745</v>
       </c>
       <c r="F37">
-        <v>3.967097944880011</v>
+        <v>3.559152721827878</v>
       </c>
       <c r="G37">
-        <v>-4.677076988185421</v>
+        <v>-3.508461033913771</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.629827613715351</v>
       </c>
       <c r="E38">
-        <v>-18.78763541330221</v>
+        <v>-19.56951267851856</v>
       </c>
       <c r="F38">
-        <v>4.113985084831103</v>
+        <v>4.118061543857445</v>
       </c>
       <c r="G38">
-        <v>-5.470644548858578</v>
+        <v>-3.262788759989995</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.617976378985453</v>
       </c>
       <c r="E39">
-        <v>-17.94864956237513</v>
+        <v>-18.04422753478102</v>
       </c>
       <c r="F39">
-        <v>4.011384697099359</v>
+        <v>4.669294143314876</v>
       </c>
       <c r="G39">
-        <v>-5.116581703433524</v>
+        <v>-4.02951772797628</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.614626750101777</v>
       </c>
       <c r="E40">
-        <v>-18.6207294468015</v>
+        <v>-19.20053714484759</v>
       </c>
       <c r="F40">
-        <v>4.556062337772786</v>
+        <v>4.533839776367341</v>
       </c>
       <c r="G40">
-        <v>-4.784212862927315</v>
+        <v>-3.753590378369105</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.630011627718419</v>
       </c>
       <c r="E41">
-        <v>-18.00388335984669</v>
+        <v>-17.79196436170974</v>
       </c>
       <c r="F41">
-        <v>4.494289888541071</v>
+        <v>3.90784833917159</v>
       </c>
       <c r="G41">
-        <v>-5.47417690094898</v>
+        <v>-4.208244150004914</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.67030981163972</v>
       </c>
       <c r="E42">
-        <v>-17.05365101644718</v>
+        <v>-15.84753272077025</v>
       </c>
       <c r="F42">
-        <v>4.394434063160783</v>
+        <v>4.378657184831175</v>
       </c>
       <c r="G42">
-        <v>-4.983904969856153</v>
+        <v>-4.171920844348031</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.744716181822126</v>
       </c>
       <c r="E43">
-        <v>-15.41353282882314</v>
+        <v>-17.20103020302681</v>
       </c>
       <c r="F43">
-        <v>4.046671248601266</v>
+        <v>3.918674552809534</v>
       </c>
       <c r="G43">
-        <v>-5.384153236099579</v>
+        <v>-4.362942632509517</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.86298950618359</v>
       </c>
       <c r="E44">
-        <v>-14.654216421113</v>
+        <v>-16.74841375443416</v>
       </c>
       <c r="F44">
-        <v>4.654977441839304</v>
+        <v>3.831307832278401</v>
       </c>
       <c r="G44">
-        <v>-5.632440840999378</v>
+        <v>-4.069005915168707</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.02425485104123</v>
       </c>
       <c r="E45">
-        <v>-14.75409191535217</v>
+        <v>-14.79715770316512</v>
       </c>
       <c r="F45">
-        <v>4.402108702027002</v>
+        <v>3.921073867271425</v>
       </c>
       <c r="G45">
-        <v>-5.698956321974415</v>
+        <v>-4.515641545508401</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.23072610169552</v>
       </c>
       <c r="E46">
-        <v>-14.38470881902051</v>
+        <v>-14.31636056082274</v>
       </c>
       <c r="F46">
-        <v>4.573034914068551</v>
+        <v>3.948936005441751</v>
       </c>
       <c r="G46">
-        <v>-5.144132063411339</v>
+        <v>-4.304316181554563</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.47987508737129</v>
       </c>
       <c r="E47">
-        <v>-13.85745406183344</v>
+        <v>-14.27833496458033</v>
       </c>
       <c r="F47">
-        <v>4.246968870550554</v>
+        <v>4.100267024191568</v>
       </c>
       <c r="G47">
-        <v>-5.884406461993309</v>
+        <v>-5.214064027382904</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.76552881748137</v>
       </c>
       <c r="E48">
-        <v>-12.45203309660493</v>
+        <v>-14.19281926141948</v>
       </c>
       <c r="F48">
-        <v>4.144727984061614</v>
+        <v>4.28014434206718</v>
       </c>
       <c r="G48">
-        <v>-4.616768780096518</v>
+        <v>-3.431040615932374</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.08398312946405</v>
       </c>
       <c r="E49">
-        <v>-12.06819058276677</v>
+        <v>-13.20799843354939</v>
       </c>
       <c r="F49">
-        <v>4.144536355645847</v>
+        <v>4.06252572852073</v>
       </c>
       <c r="G49">
-        <v>-4.652797447200406</v>
+        <v>-3.74357597811281</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.42580457383963</v>
       </c>
       <c r="E50">
-        <v>-12.25243607624285</v>
+        <v>-12.94837196174163</v>
       </c>
       <c r="F50">
-        <v>4.348134420722911</v>
+        <v>3.964731888242344</v>
       </c>
       <c r="G50">
-        <v>-5.20653915737214</v>
+        <v>-4.443325988748561</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.78590298528351</v>
       </c>
       <c r="E51">
-        <v>-11.13738086438616</v>
+        <v>-12.22534674472897</v>
       </c>
       <c r="F51">
-        <v>4.334691924912661</v>
+        <v>4.167520679596619</v>
       </c>
       <c r="G51">
-        <v>-5.244137023061644</v>
+        <v>-3.17418862972248</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.16252944555008</v>
       </c>
       <c r="E52">
-        <v>-10.67966082558687</v>
+        <v>-12.23497428046927</v>
       </c>
       <c r="F52">
-        <v>3.861960460271732</v>
+        <v>4.001630652366168</v>
       </c>
       <c r="G52">
-        <v>-5.068403334200511</v>
+        <v>-4.324119864970484</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.54737420999723</v>
       </c>
       <c r="E53">
-        <v>-10.28849124080431</v>
+        <v>-12.60171727645447</v>
       </c>
       <c r="F53">
-        <v>4.134406972610695</v>
+        <v>4.00926253117267</v>
       </c>
       <c r="G53">
-        <v>-4.916035475755554</v>
+        <v>-4.145198120755033</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.94407080730288</v>
       </c>
       <c r="E54">
-        <v>-10.19529977420046</v>
+        <v>-11.10053719985976</v>
       </c>
       <c r="F54">
-        <v>3.967847037778013</v>
+        <v>3.483150674945939</v>
       </c>
       <c r="G54">
-        <v>-5.729724532216402</v>
+        <v>-3.504971718915379</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.35550948212003</v>
       </c>
       <c r="E55">
-        <v>-8.365058133838385</v>
+        <v>-9.113356764287859</v>
       </c>
       <c r="F55">
-        <v>4.108600484718609</v>
+        <v>4.00005644868622</v>
       </c>
       <c r="G55">
-        <v>-5.815398140227201</v>
+        <v>-3.837343869967127</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.78045785196786</v>
       </c>
       <c r="E56">
-        <v>-8.670417664649605</v>
+        <v>-9.913805301409663</v>
       </c>
       <c r="F56">
-        <v>3.9541416467858</v>
+        <v>3.736249052115979</v>
       </c>
       <c r="G56">
-        <v>-5.63007049039326</v>
+        <v>-4.366481605690998</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.22563406797255</v>
       </c>
       <c r="E57">
-        <v>-9.085429665082556</v>
+        <v>-8.941985722415589</v>
       </c>
       <c r="F57">
-        <v>4.436435527744153</v>
+        <v>3.926110052082522</v>
       </c>
       <c r="G57">
-        <v>-5.552213080400681</v>
+        <v>-3.941722060274808</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.68988062928078</v>
       </c>
       <c r="E58">
-        <v>-8.215853972233663</v>
+        <v>-9.534215024664711</v>
       </c>
       <c r="F58">
-        <v>4.085318424055735</v>
+        <v>4.105984202546304</v>
       </c>
       <c r="G58">
-        <v>-5.47376639330211</v>
+        <v>-4.391423255783867</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.17103178206766</v>
       </c>
       <c r="E59">
-        <v>-8.309588855718431</v>
+        <v>-8.748701394820204</v>
       </c>
       <c r="F59">
-        <v>4.112436220445804</v>
+        <v>3.729896807689152</v>
       </c>
       <c r="G59">
-        <v>-5.313569094656778</v>
+        <v>-4.05468118462028</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.66657557505579</v>
       </c>
       <c r="E60">
-        <v>-8.342750870876602</v>
+        <v>-7.555267354838757</v>
       </c>
       <c r="F60">
-        <v>3.802970582333443</v>
+        <v>3.724138452980614</v>
       </c>
       <c r="G60">
-        <v>-5.696827641192664</v>
+        <v>-4.530486031706492</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.16257211227858</v>
       </c>
       <c r="E61">
-        <v>-7.430453554239347</v>
+        <v>-6.836711741671663</v>
       </c>
       <c r="F61">
-        <v>4.087581539808897</v>
+        <v>4.145443819135393</v>
       </c>
       <c r="G61">
-        <v>-6.154090122713418</v>
+        <v>-3.810568177645502</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.64835787220616</v>
       </c>
       <c r="E62">
-        <v>-7.516843252883675</v>
+        <v>-8.70499256369817</v>
       </c>
       <c r="F62">
-        <v>4.023797784064573</v>
+        <v>3.723284835492192</v>
       </c>
       <c r="G62">
-        <v>-6.238042247043796</v>
+        <v>-4.676408257986488</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.11284213976611</v>
       </c>
       <c r="E63">
-        <v>-7.211800715252991</v>
+        <v>-7.289717639028968</v>
       </c>
       <c r="F63">
-        <v>4.01742336775493</v>
+        <v>3.053776327151997</v>
       </c>
       <c r="G63">
-        <v>-6.208174505188492</v>
+        <v>-5.505170228287637</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.53531463761885</v>
       </c>
       <c r="E64">
-        <v>-6.477214304098744</v>
+        <v>-6.492814897055169</v>
       </c>
       <c r="F64">
-        <v>4.140836818627379</v>
+        <v>3.453202796084979</v>
       </c>
       <c r="G64">
-        <v>-5.865754848425055</v>
+        <v>-4.959824061603494</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.90643247787688</v>
       </c>
       <c r="E65">
-        <v>-7.001761033829225</v>
+        <v>-7.226726565582273</v>
       </c>
       <c r="F65">
-        <v>3.846772720542667</v>
+        <v>3.994925241520197</v>
       </c>
       <c r="G65">
-        <v>-5.876206240692534</v>
+        <v>-5.353318814946807</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.21553021125637</v>
       </c>
       <c r="E66">
-        <v>-6.020033153706368</v>
+        <v>-5.933367218147573</v>
       </c>
       <c r="F66">
-        <v>4.155530442110827</v>
+        <v>3.249791608305937</v>
       </c>
       <c r="G66">
-        <v>-6.050960008074042</v>
+        <v>-4.454174646480753</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.45071363540432</v>
       </c>
       <c r="E67">
-        <v>-6.640429564283199</v>
+        <v>-6.579358563815757</v>
       </c>
       <c r="F67">
-        <v>4.036781005159346</v>
+        <v>3.479021953624389</v>
       </c>
       <c r="G67">
-        <v>-5.685475780538503</v>
+        <v>-4.441783274527261</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.60828305914176</v>
       </c>
       <c r="E68">
-        <v>-7.074153219315844</v>
+        <v>-6.841235687205326</v>
       </c>
       <c r="F68">
-        <v>3.846525662419859</v>
+        <v>3.335481184272619</v>
       </c>
       <c r="G68">
-        <v>-5.875938086503853</v>
+        <v>-4.774599038681272</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.68465321411706</v>
       </c>
       <c r="E69">
-        <v>-6.882481028467188</v>
+        <v>-6.399383421328914</v>
       </c>
       <c r="F69">
-        <v>3.533892612476619</v>
+        <v>3.582640664259761</v>
       </c>
       <c r="G69">
-        <v>-5.859216520984994</v>
+        <v>-5.356205610657051</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.6800181303177</v>
       </c>
       <c r="E70">
-        <v>-5.697152956959472</v>
+        <v>-6.307822205367827</v>
       </c>
       <c r="F70">
-        <v>3.553823551422425</v>
+        <v>3.041507357425087</v>
       </c>
       <c r="G70">
-        <v>-6.251006343375582</v>
+        <v>-4.731608294308296</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.60247861898645</v>
       </c>
       <c r="E71">
-        <v>-6.377424850865721</v>
+        <v>-8.210945106409348</v>
       </c>
       <c r="F71">
-        <v>3.351691998023057</v>
+        <v>3.196702618608576</v>
       </c>
       <c r="G71">
-        <v>-5.400788727434416</v>
+        <v>-4.346548810999046</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.45823935279897</v>
       </c>
       <c r="E72">
-        <v>-6.056433027780022</v>
+        <v>-6.323178260727837</v>
       </c>
       <c r="F72">
-        <v>3.300881961138014</v>
+        <v>3.210458688190083</v>
       </c>
       <c r="G72">
-        <v>-5.469078660818503</v>
+        <v>-4.124944203145772</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.25719539016752</v>
       </c>
       <c r="E73">
-        <v>-6.957526899722301</v>
+        <v>-7.712079352776366</v>
       </c>
       <c r="F73">
-        <v>3.252727799073162</v>
+        <v>3.201224098997155</v>
       </c>
       <c r="G73">
-        <v>-5.167997786203945</v>
+        <v>-4.310669118444425</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.01732547532047</v>
       </c>
       <c r="E74">
-        <v>-6.43163974168555</v>
+        <v>-5.601860278416064</v>
       </c>
       <c r="F74">
-        <v>3.271545392760413</v>
+        <v>2.998603180469917</v>
       </c>
       <c r="G74">
-        <v>-5.533511808649338</v>
+        <v>-4.248430862306127</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.74796105218515</v>
       </c>
       <c r="E75">
-        <v>-7.593071055854789</v>
+        <v>-9.398143437682233</v>
       </c>
       <c r="F75">
-        <v>3.162206336358474</v>
+        <v>3.136363423230333</v>
       </c>
       <c r="G75">
-        <v>-5.110089723631013</v>
+        <v>-3.928648715940227</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.46274082311052</v>
       </c>
       <c r="E76">
-        <v>-8.262913874121374</v>
+        <v>-7.396009980937007</v>
       </c>
       <c r="F76">
-        <v>2.892998502616584</v>
+        <v>2.711765532477355</v>
       </c>
       <c r="G76">
-        <v>-5.225316571670887</v>
+        <v>-4.449384287085427</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.17752399813537</v>
       </c>
       <c r="E77">
-        <v>-7.715507407600173</v>
+        <v>-6.927869923446067</v>
       </c>
       <c r="F77">
-        <v>2.777425979731475</v>
+        <v>2.917519021305333</v>
       </c>
       <c r="G77">
-        <v>-5.012895417143551</v>
+        <v>-3.903395874566666</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.90051794398405</v>
       </c>
       <c r="E78">
-        <v>-8.073619132126744</v>
+        <v>-8.185911702094947</v>
       </c>
       <c r="F78">
-        <v>3.169002018441625</v>
+        <v>2.766796145627045</v>
       </c>
       <c r="G78">
-        <v>-4.334753337242623</v>
+        <v>-3.381875704128658</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.64126779157847</v>
       </c>
       <c r="E79">
-        <v>-8.404184149264658</v>
+        <v>-10.04667978574273</v>
       </c>
       <c r="F79">
-        <v>2.947801062114451</v>
+        <v>2.454451330160416</v>
       </c>
       <c r="G79">
-        <v>-4.725996919619231</v>
+        <v>-4.649480280570057</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.40519053045939</v>
       </c>
       <c r="E80">
-        <v>-9.987411117930337</v>
+        <v>-8.551644848376428</v>
       </c>
       <c r="F80">
-        <v>2.884943774330659</v>
+        <v>2.573325879879216</v>
       </c>
       <c r="G80">
-        <v>-4.291335532495081</v>
+        <v>-3.218374481035132</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.19083298630709</v>
       </c>
       <c r="E81">
-        <v>-10.57568253389675</v>
+        <v>-10.56983627395285</v>
       </c>
       <c r="F81">
-        <v>3.036391987318218</v>
+        <v>2.477484748994567</v>
       </c>
       <c r="G81">
-        <v>-4.898671664402077</v>
+        <v>-2.505312766785972</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.00031866194907</v>
       </c>
       <c r="E82">
-        <v>-10.66518782265836</v>
+        <v>-11.52741833066681</v>
       </c>
       <c r="F82">
-        <v>2.820792598813953</v>
+        <v>2.012345570512255</v>
       </c>
       <c r="G82">
-        <v>-4.309550154052151</v>
+        <v>-3.119422274866317</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.82765051843433</v>
       </c>
       <c r="E83">
-        <v>-12.14200018061779</v>
+        <v>-11.04781670546246</v>
       </c>
       <c r="F83">
-        <v>2.688557905992506</v>
+        <v>2.042689375852075</v>
       </c>
       <c r="G83">
-        <v>-3.749289979713592</v>
+        <v>-3.278964085494874</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-15.66761344166629</v>
       </c>
       <c r="E84">
-        <v>-11.9987736047032</v>
+        <v>-13.28277712483805</v>
       </c>
       <c r="F84">
-        <v>2.753318808286656</v>
+        <v>2.254617734044351</v>
       </c>
       <c r="G84">
-        <v>-3.88847855636671</v>
+        <v>-3.092325459627382</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-15.52435482445723</v>
       </c>
       <c r="E85">
-        <v>-14.49876296537769</v>
+        <v>-13.48953819108026</v>
       </c>
       <c r="F85">
-        <v>2.711477298000745</v>
+        <v>1.940358218125955</v>
       </c>
       <c r="G85">
-        <v>-3.88638629158589</v>
+        <v>-3.02828957726126</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-15.39302517834636</v>
       </c>
       <c r="E86">
-        <v>-15.34625781896519</v>
+        <v>-15.44976514935851</v>
       </c>
       <c r="F86">
-        <v>2.548553551949912</v>
+        <v>1.820782086686615</v>
       </c>
       <c r="G86">
-        <v>-3.897254812591318</v>
+        <v>-1.126907541690707</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-15.27544825334024</v>
       </c>
       <c r="E87">
-        <v>-16.77281317238749</v>
+        <v>-17.07736210635134</v>
       </c>
       <c r="F87">
-        <v>2.446461533817024</v>
+        <v>1.992851734399111</v>
       </c>
       <c r="G87">
-        <v>-2.624687728386552</v>
+        <v>-2.879990379284068</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-15.17628773812683</v>
       </c>
       <c r="E88">
-        <v>-16.80946664100558</v>
+        <v>-17.10606810308596</v>
       </c>
       <c r="F88">
-        <v>2.335530852970067</v>
+        <v>1.826811255106693</v>
       </c>
       <c r="G88">
-        <v>-2.782286248783557</v>
+        <v>-1.831255900080505</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-15.09735254964008</v>
       </c>
       <c r="E89">
-        <v>-19.36937224127556</v>
+        <v>-19.86109206292444</v>
       </c>
       <c r="F89">
-        <v>2.346003900188868</v>
+        <v>1.688838795753608</v>
       </c>
       <c r="G89">
-        <v>-2.38208764072322</v>
+        <v>-1.866000075515156</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-15.04650472557571</v>
       </c>
       <c r="E90">
-        <v>-20.41256962757853</v>
+        <v>-20.99488610022487</v>
       </c>
       <c r="F90">
-        <v>1.882646390861426</v>
+        <v>1.637233738499014</v>
       </c>
       <c r="G90">
-        <v>-2.481682092726655</v>
+        <v>-1.139725974018765</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-15.02737100901333</v>
       </c>
       <c r="E91">
-        <v>-22.37372945150236</v>
+        <v>-22.83130910760741</v>
       </c>
       <c r="F91">
-        <v>1.699555733683387</v>
+        <v>1.206084056373863</v>
       </c>
       <c r="G91">
-        <v>-1.758814542590173</v>
+        <v>-1.721508004908126</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-15.04255265539332</v>
       </c>
       <c r="E92">
-        <v>-23.87892175606786</v>
+        <v>-24.41645614925234</v>
       </c>
       <c r="F92">
-        <v>1.831747666445118</v>
+        <v>1.149137159066491</v>
       </c>
       <c r="G92">
-        <v>-2.292004386054112</v>
+        <v>-0.6184905104971342</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-15.09882063569847</v>
       </c>
       <c r="E93">
-        <v>-27.12933812997544</v>
+        <v>-28.47653197641333</v>
       </c>
       <c r="F93">
-        <v>1.217268187548696</v>
+        <v>1.124136777485364</v>
       </c>
       <c r="G93">
-        <v>-1.534309896844497</v>
+        <v>-0.6334243814247865</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-15.19044063883731</v>
       </c>
       <c r="E94">
-        <v>-28.40951508957381</v>
+        <v>-30.88655414397743</v>
       </c>
       <c r="F94">
-        <v>1.154838500362073</v>
+        <v>1.123804199243122</v>
       </c>
       <c r="G94">
-        <v>-1.682466741363501</v>
+        <v>-1.638065704590796</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.31532636420521</v>
       </c>
       <c r="E95">
-        <v>-30.73617257913072</v>
+        <v>-31.19963698720874</v>
       </c>
       <c r="F95">
-        <v>0.8401054563749611</v>
+        <v>1.066307755983093</v>
       </c>
       <c r="G95">
-        <v>-2.4925605453687</v>
+        <v>-0.9588145919342121</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-15.47023732763857</v>
       </c>
       <c r="E96">
-        <v>-32.51861391210483</v>
+        <v>-34.19373041109715</v>
       </c>
       <c r="F96">
-        <v>0.723134521166519</v>
+        <v>0.8045290866905294</v>
       </c>
       <c r="G96">
-        <v>-2.256197525501355</v>
+        <v>-0.8778088531337855</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.64096191605463</v>
       </c>
       <c r="E97">
-        <v>-34.91653373288344</v>
+        <v>-35.96218781633558</v>
       </c>
       <c r="F97">
-        <v>0.5568865763991785</v>
+        <v>0.7253596279777115</v>
       </c>
       <c r="G97">
-        <v>-2.28833299105106</v>
+        <v>-1.173235315967268</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.82089713165476</v>
       </c>
       <c r="E98">
-        <v>-39.12555786286771</v>
+        <v>-39.01713260970206</v>
       </c>
       <c r="F98">
-        <v>0.2055430027648525</v>
+        <v>0.5940799098232739</v>
       </c>
       <c r="G98">
-        <v>-1.740944217769187</v>
+        <v>-2.301419577567799</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.99525582604107</v>
       </c>
       <c r="E99">
-        <v>-40.57460614668612</v>
+        <v>-42.18844786388065</v>
       </c>
       <c r="F99">
-        <v>-0.01163296497823211</v>
+        <v>0.2698200829018356</v>
       </c>
       <c r="G99">
-        <v>-2.312668811310242</v>
+        <v>-1.327556396280394</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.15699730699081</v>
       </c>
       <c r="E100">
-        <v>-44.44822432081828</v>
+        <v>-43.89961554444804</v>
       </c>
       <c r="F100">
-        <v>-0.1574431849068266</v>
+        <v>0.1034882017209768</v>
       </c>
       <c r="G100">
-        <v>-2.433361370035452</v>
+        <v>-2.383795882221484</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.290973299903</v>
       </c>
       <c r="E101">
-        <v>-46.39702141070116</v>
+        <v>-46.87120018828133</v>
       </c>
       <c r="F101">
-        <v>-0.4856139735864426</v>
+        <v>0.2180328994669657</v>
       </c>
       <c r="G101">
-        <v>-3.109487327702964</v>
+        <v>-1.770507389434879</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.40370849549277</v>
       </c>
       <c r="E102">
-        <v>-48.77152902086011</v>
+        <v>-49.24734031332005</v>
       </c>
       <c r="F102">
-        <v>-0.5173411460433988</v>
+        <v>-0.2420986009107268</v>
       </c>
       <c r="G102">
-        <v>-2.758586053267914</v>
+        <v>-2.060246335031893</v>
       </c>
     </row>
   </sheetData>
